--- a/docs/01_db/テーブル定義書.xlsx
+++ b/docs/01_db/テーブル定義書.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC9C96C-900E-4B39-A2AE-43835D5CFAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{450BDAA2-F2F9-4910-B507-30479056A808}"/>
+    <workbookView xWindow="3700" yWindow="1620" windowWidth="14400" windowHeight="7270" xr2:uid="{450BDAA2-F2F9-4910-B507-30479056A808}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル定義書" sheetId="1" r:id="rId1"/>
@@ -237,7 +237,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -256,11 +256,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -742,18 +739,18 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6"/>

--- a/docs/01_db/テーブル定義書.xlsx
+++ b/docs/01_db/テーブル定義書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC9C96C-900E-4B39-A2AE-43835D5CFAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A51B7F-4FE5-400E-8C7B-275547EC393D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3700" yWindow="1620" windowWidth="14400" windowHeight="7270" xr2:uid="{450BDAA2-F2F9-4910-B507-30479056A808}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{450BDAA2-F2F9-4910-B507-30479056A808}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル定義書" sheetId="1" r:id="rId1"/>
@@ -142,11 +142,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>VARCHAR</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>INT</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VARCHAR</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
@@ -676,7 +676,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -693,7 +693,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
@@ -706,7 +706,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>16</v>
@@ -721,7 +721,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
